--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A932ABBC-2923-4363-8EE4-DA93156AB1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7A99A4-846A-468B-B35C-E85103BB2EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2204,26 +2204,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B31" s="14">
+        <v>255</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>70</v>
+      </c>
+      <c r="E31" s="14">
+        <v>110</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>250</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>715</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>725</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7A99A4-846A-468B-B35C-E85103BB2EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E825EE4B-EBBA-4129-8C7D-E062247EAD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t xml:space="preserve">CA </t>
+  </si>
+  <si>
+    <t>Average day</t>
   </si>
 </sst>
 </file>
@@ -2250,26 +2253,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B32" s="14">
+        <v>350</v>
+      </c>
+      <c r="C32" s="14">
+        <v>20</v>
+      </c>
+      <c r="D32" s="14">
+        <v>150</v>
+      </c>
+      <c r="E32" s="14">
+        <v>90</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>360</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E825EE4B-EBBA-4129-8C7D-E062247EAD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE054FAD-0D22-457B-B0DB-E92ECBCF10D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2299,26 +2299,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B33" s="14">
+        <v>322</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>50</v>
+      </c>
+      <c r="E33" s="14">
+        <v>70</v>
+      </c>
+      <c r="F33" s="14">
+        <v>300</v>
+      </c>
+      <c r="G33" s="14">
+        <v>6</v>
+      </c>
+      <c r="H33" s="14">
+        <v>255</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1027</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>413</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE054FAD-0D22-457B-B0DB-E92ECBCF10D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6ABCA7-8682-44FB-A361-4C5F518278A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2345,26 +2345,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>39717</v>
+      </c>
+      <c r="B34" s="14">
+        <v>250</v>
+      </c>
+      <c r="C34" s="14">
+        <v>20</v>
+      </c>
+      <c r="D34" s="14">
+        <v>80</v>
+      </c>
+      <c r="E34" s="14">
+        <v>45</v>
+      </c>
+      <c r="F34" s="14">
+        <v>350</v>
+      </c>
+      <c r="G34" s="14">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14">
+        <v>300</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1045</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>395</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6ABCA7-8682-44FB-A361-4C5F518278A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C103932-E12B-4274-BA04-4CD3EE6439FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Average day</t>
+  </si>
+  <si>
+    <t>Prepare for next  CA</t>
   </si>
 </sst>
 </file>
@@ -2346,7 +2349,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13">
-        <v>39717</v>
+        <v>46273</v>
       </c>
       <c r="B34" s="14">
         <v>250</v>
@@ -2391,26 +2394,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B35" s="14">
+        <v>300</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>40</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>6</v>
+      </c>
+      <c r="H35" s="14">
+        <v>250</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C103932-E12B-4274-BA04-4CD3EE6439FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05028906-F4E4-440A-82D5-C98785A71473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Prepare for next  CA</t>
+  </si>
+  <si>
+    <t>prepare for next ca</t>
   </si>
 </sst>
 </file>
@@ -2440,48 +2443,96 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B36" s="14">
+        <v>220</v>
+      </c>
+      <c r="C36" s="14">
+        <v>40</v>
+      </c>
+      <c r="D36" s="14">
+        <v>65</v>
+      </c>
+      <c r="E36" s="14">
+        <v>40</v>
+      </c>
+      <c r="F36" s="14">
+        <v>150</v>
+      </c>
+      <c r="G36" s="14">
+        <v>3</v>
+      </c>
+      <c r="H36" s="14">
+        <v>300</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>815</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>625</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B37" s="14">
+        <v>300</v>
+      </c>
+      <c r="C37" s="14">
+        <v>30</v>
+      </c>
+      <c r="D37" s="14">
+        <v>40</v>
+      </c>
+      <c r="E37" s="14">
+        <v>60</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>200</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05028906-F4E4-440A-82D5-C98785A71473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFB0919-E76A-4F7F-9F39-FADBFEB7230C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>prepare for next ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Busy </t>
   </si>
 </sst>
 </file>
@@ -2535,48 +2538,96 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B38" s="14">
+        <v>300</v>
+      </c>
+      <c r="C38" s="14">
+        <v>20</v>
+      </c>
+      <c r="D38" s="14">
+        <v>50</v>
+      </c>
+      <c r="E38" s="14">
+        <v>80</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>400</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B39" s="14">
+        <v>240</v>
+      </c>
+      <c r="C39" s="14">
+        <v>50</v>
+      </c>
+      <c r="D39" s="14">
+        <v>60</v>
+      </c>
+      <c r="E39" s="14">
+        <v>100</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>350</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFB0919-E76A-4F7F-9F39-FADBFEB7230C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6F4308-F60A-4252-8B46-74BB095F9BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,15 @@
   </si>
   <si>
     <t xml:space="preserve">Busy </t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>New Week</t>
   </si>
 </sst>
 </file>
@@ -2585,7 +2594,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13">
-        <v>46268</v>
+        <v>46278</v>
       </c>
       <c r="B39" s="14">
         <v>240</v>
@@ -2630,26 +2639,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B40" s="14">
+        <v>250</v>
+      </c>
+      <c r="C40" s="14">
+        <v>30</v>
+      </c>
+      <c r="D40" s="14">
+        <v>50</v>
+      </c>
+      <c r="E40" s="14">
+        <v>180</v>
+      </c>
+      <c r="F40" s="14">
+        <v>300</v>
+      </c>
+      <c r="G40" s="14">
+        <v>6</v>
+      </c>
+      <c r="H40" s="14">
+        <v>370</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6F4308-F60A-4252-8B46-74BB095F9BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B86CA2-EF9A-45E6-A3E6-6A4360B53ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>New Week</t>
+  </si>
+  <si>
+    <t>Prepare for next CA</t>
   </si>
 </sst>
 </file>
@@ -2685,26 +2688,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B41" s="14">
+        <v>300</v>
+      </c>
+      <c r="C41" s="14">
+        <v>60</v>
+      </c>
+      <c r="D41" s="14">
+        <v>50</v>
+      </c>
+      <c r="E41" s="14">
+        <v>60</v>
+      </c>
+      <c r="F41" s="14">
+        <v>350</v>
+      </c>
+      <c r="G41" s="14">
+        <v>7</v>
+      </c>
+      <c r="H41" s="14">
+        <v>400</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B86CA2-EF9A-45E6-A3E6-6A4360B53ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31112379-8C5A-4757-A0D9-D0D6E8C5594B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2734,26 +2734,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B42" s="14">
+        <v>250</v>
+      </c>
+      <c r="C42" s="14">
+        <v>50</v>
+      </c>
+      <c r="D42" s="14">
+        <v>65</v>
+      </c>
+      <c r="E42" s="14">
+        <v>50</v>
+      </c>
+      <c r="F42" s="14">
+        <v>300</v>
+      </c>
+      <c r="G42" s="14">
+        <v>5</v>
+      </c>
+      <c r="H42" s="14">
+        <v>300</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>425</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31112379-8C5A-4757-A0D9-D0D6E8C5594B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DD9C00-4504-431C-B394-CA7AE34B2D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>Prepare for next CA</t>
+  </si>
+  <si>
+    <t>Tommorow is CA</t>
   </si>
 </sst>
 </file>
@@ -2780,26 +2783,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B43" s="14">
+        <v>200</v>
+      </c>
+      <c r="C43" s="14">
+        <v>305</v>
+      </c>
+      <c r="D43" s="14">
+        <v>80</v>
+      </c>
+      <c r="E43" s="14">
+        <v>60</v>
+      </c>
+      <c r="F43" s="14">
+        <v>150</v>
+      </c>
+      <c r="G43" s="14">
+        <v>3</v>
+      </c>
+      <c r="H43" s="14">
+        <v>400</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1195</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>245</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DD9C00-4504-431C-B394-CA7AE34B2D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3100B25-1F0E-461B-896D-96BF76632EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>Tommorow is CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DBMS CA2 OVER </t>
   </si>
 </sst>
 </file>
@@ -2790,7 +2793,7 @@
         <v>200</v>
       </c>
       <c r="C43" s="14">
-        <v>305</v>
+        <v>30</v>
       </c>
       <c r="D43" s="14">
         <v>80</v>
@@ -2809,11 +2812,11 @@
       </c>
       <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v>1195</v>
+        <v>920</v>
       </c>
       <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v>245</v>
+        <v>520</v>
       </c>
       <c r="K43" s="16" t="s">
         <v>84</v>
@@ -2829,26 +2832,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B44" s="14">
+        <v>400</v>
+      </c>
+      <c r="C44" s="14">
+        <v>60</v>
+      </c>
+      <c r="D44" s="14">
+        <v>66</v>
+      </c>
+      <c r="E44" s="14">
+        <v>82</v>
+      </c>
+      <c r="F44" s="14">
+        <v>250</v>
+      </c>
+      <c r="G44" s="14">
+        <v>5</v>
+      </c>
+      <c r="H44" s="14">
+        <v>450</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1308</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>132</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3100B25-1F0E-461B-896D-96BF76632EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618FA402-3BA4-4056-8EA9-AC3FF6F23139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2878,26 +2878,50 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B45" s="14">
+        <v>200</v>
+      </c>
+      <c r="C45" s="14">
+        <v>60</v>
+      </c>
+      <c r="D45" s="14">
+        <v>120</v>
+      </c>
+      <c r="E45" s="14">
+        <v>80</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>400</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618FA402-3BA4-4056-8EA9-AC3FF6F23139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9A698D-08E6-4C21-9EAC-46E76D02858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2924,26 +2924,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B46" s="14">
+        <v>300</v>
+      </c>
+      <c r="C46" s="14">
+        <v>70</v>
+      </c>
+      <c r="D46" s="14">
+        <v>60</v>
+      </c>
+      <c r="E46" s="14">
+        <v>50</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>500</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9A698D-08E6-4C21-9EAC-46E76D02858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC82622-D193-48E0-8204-DF5FADB8E932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,12 @@
   </si>
   <si>
     <t xml:space="preserve">DBMS CA2 OVER </t>
+  </si>
+  <si>
+    <t>prepare for english &amp; network ca</t>
+  </si>
+  <si>
+    <t>study</t>
   </si>
 </sst>
 </file>
@@ -2970,48 +2976,96 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B47" s="14">
+        <v>400</v>
+      </c>
+      <c r="C47" s="14">
+        <v>20</v>
+      </c>
+      <c r="D47" s="14">
+        <v>90</v>
+      </c>
+      <c r="E47" s="14">
+        <v>50</v>
+      </c>
+      <c r="F47" s="14">
+        <v>300</v>
+      </c>
+      <c r="G47" s="14">
+        <v>6</v>
+      </c>
+      <c r="H47" s="14">
+        <v>450</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B48" s="14">
+        <v>430</v>
+      </c>
+      <c r="C48" s="14">
+        <v>30</v>
+      </c>
+      <c r="D48" s="14">
+        <v>80</v>
+      </c>
+      <c r="E48" s="14">
+        <v>70</v>
+      </c>
+      <c r="F48" s="14">
+        <v>350</v>
+      </c>
+      <c r="G48" s="14">
+        <v>7</v>
+      </c>
+      <c r="H48" s="14">
+        <v>350</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC82622-D193-48E0-8204-DF5FADB8E932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8FA796-59E2-42E2-A8BC-F0135EB3ED48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3068,26 +3068,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B49" s="14">
+        <v>300</v>
+      </c>
+      <c r="C49" s="14">
+        <v>50</v>
+      </c>
+      <c r="D49" s="14">
+        <v>80</v>
+      </c>
+      <c r="E49" s="14">
+        <v>90</v>
+      </c>
+      <c r="F49" s="14">
+        <v>300</v>
+      </c>
+      <c r="G49" s="14">
+        <v>6</v>
+      </c>
+      <c r="H49" s="14">
+        <v>400</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8FA796-59E2-42E2-A8BC-F0135EB3ED48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4223790D-1912-4A3A-BCF0-975E8D78D6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>study</t>
+  </si>
+  <si>
+    <t>Focus on study</t>
   </si>
 </sst>
 </file>
@@ -3114,26 +3117,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B50" s="14">
+        <v>350</v>
+      </c>
+      <c r="C50" s="14">
+        <v>60</v>
+      </c>
+      <c r="D50" s="14">
+        <v>90</v>
+      </c>
+      <c r="E50" s="14">
+        <v>120</v>
+      </c>
+      <c r="F50" s="14">
+        <v>100</v>
+      </c>
+      <c r="G50" s="14">
+        <v>2</v>
+      </c>
+      <c r="H50" s="14">
+        <v>350</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4223790D-1912-4A3A-BCF0-975E8D78D6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874B77CC-DD52-48D2-8EF5-DBDDA7A3E311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3163,26 +3163,50 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B51" s="14">
+        <v>450</v>
+      </c>
+      <c r="C51" s="14">
+        <v>30</v>
+      </c>
+      <c r="D51" s="14">
+        <v>120</v>
+      </c>
+      <c r="E51" s="14">
+        <v>30</v>
+      </c>
+      <c r="F51" s="14">
+        <v>250</v>
+      </c>
+      <c r="G51" s="14">
+        <v>5</v>
+      </c>
+      <c r="H51" s="14">
+        <v>250</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874B77CC-DD52-48D2-8EF5-DBDDA7A3E311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E14A88D-9559-4CA0-8D23-F6B1CAD8F42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>Focus on study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lots of study </t>
   </si>
 </sst>
 </file>
@@ -3209,26 +3212,50 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B52" s="14">
+        <v>400</v>
+      </c>
+      <c r="C52" s="14">
+        <v>20</v>
+      </c>
+      <c r="D52" s="14">
+        <v>60</v>
+      </c>
+      <c r="E52" s="14">
+        <v>90</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>300</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E14A88D-9559-4CA0-8D23-F6B1CAD8F42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A72ED9-75C9-42D0-BAC1-63AB527CFFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,12 @@
   </si>
   <si>
     <t xml:space="preserve">Lots of study </t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Bad day</t>
   </si>
 </sst>
 </file>
@@ -3258,26 +3264,50 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B53" s="14">
+        <v>600</v>
+      </c>
+      <c r="C53" s="14">
+        <v>30</v>
+      </c>
+      <c r="D53" s="14">
+        <v>20</v>
+      </c>
+      <c r="E53" s="14">
+        <v>30</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>400</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A72ED9-75C9-42D0-BAC1-63AB527CFFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F48346-C490-4DD7-9C8C-504AFAEFF777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3310,26 +3310,50 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B54" s="14">
+        <v>500</v>
+      </c>
+      <c r="C54" s="14">
+        <v>60</v>
+      </c>
+      <c r="D54" s="14">
+        <v>200</v>
+      </c>
+      <c r="E54" s="14">
+        <v>120</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>425</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1305</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>135</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F48346-C490-4DD7-9C8C-504AFAEFF777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236E0D02-822B-4336-9A37-368D4606A347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>Bad day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good day </t>
   </si>
 </sst>
 </file>
@@ -3356,26 +3359,50 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B55" s="14">
+        <v>450</v>
+      </c>
+      <c r="C55" s="14">
+        <v>20</v>
+      </c>
+      <c r="D55" s="14">
+        <v>50</v>
+      </c>
+      <c r="E55" s="14">
+        <v>90</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>400</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236E0D02-822B-4336-9A37-368D4606A347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1E6BA2-54E5-4810-B20A-737296EE0742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,12 @@
   </si>
   <si>
     <t xml:space="preserve">Good day </t>
+  </si>
+  <si>
+    <t>On a journey</t>
+  </si>
+  <si>
+    <t>Travelling</t>
   </si>
 </sst>
 </file>
@@ -3405,48 +3411,92 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B56" s="14">
+        <v>500</v>
+      </c>
+      <c r="C56" s="14">
+        <v>60</v>
+      </c>
+      <c r="D56" s="14">
+        <v>65</v>
+      </c>
+      <c r="E56" s="14">
+        <v>80</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>360</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1065</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>375</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
+      <c r="A57" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B57" s="14">
+        <v>400</v>
+      </c>
+      <c r="C57" s="14">
+        <v>300</v>
+      </c>
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
       <c r="F57" s="14"/>
       <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="H57" s="14">
+        <v>600</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1E6BA2-54E5-4810-B20A-737296EE0742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530514BB-F12B-49BD-AEAB-EAE4ACFB1137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>Travelling</t>
+  </si>
+  <si>
+    <t>Rest Day</t>
   </si>
 </sst>
 </file>
@@ -3472,8 +3475,12 @@
       <c r="E57" s="14">
         <v>0</v>
       </c>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
       <c r="H57" s="14">
         <v>600</v>
       </c>
@@ -3499,26 +3506,50 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B58" s="14">
+        <v>600</v>
+      </c>
+      <c r="C58" s="14">
+        <v>30</v>
+      </c>
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>300</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530514BB-F12B-49BD-AEAB-EAE4ACFB1137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27016D3-C3D6-45B1-B9D5-9AC6C2555BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3552,26 +3552,50 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B59" s="14">
+        <v>500</v>
+      </c>
+      <c r="C59" s="14">
+        <v>40</v>
+      </c>
+      <c r="D59" s="14">
+        <v>60</v>
+      </c>
+      <c r="E59" s="14">
+        <v>400</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>400</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27016D3-C3D6-45B1-B9D5-9AC6C2555BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923A9F21-C42B-4381-8F06-6DC6497838C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>Rest Day</t>
+  </si>
+  <si>
+    <t>Prepare  for exam</t>
   </si>
 </sst>
 </file>
@@ -3598,26 +3601,50 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B60" s="14">
+        <v>400</v>
+      </c>
+      <c r="C60" s="14">
+        <v>60</v>
+      </c>
+      <c r="D60" s="14">
+        <v>80</v>
+      </c>
+      <c r="E60" s="14">
+        <v>110</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>350</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923A9F21-C42B-4381-8F06-6DC6497838C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A166A7D5-6EE6-4086-8AED-0FE7228FE728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>Prepare  for exam</t>
+  </si>
+  <si>
+    <t>Start study</t>
   </si>
 </sst>
 </file>
@@ -3647,26 +3650,50 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B61" s="14">
+        <v>450</v>
+      </c>
+      <c r="C61" s="14">
+        <v>80</v>
+      </c>
+      <c r="D61" s="14">
+        <v>60</v>
+      </c>
+      <c r="E61" s="14">
+        <v>50</v>
+      </c>
+      <c r="F61" s="14">
+        <v>300</v>
+      </c>
+      <c r="G61" s="14">
+        <v>6</v>
+      </c>
+      <c r="H61" s="14">
+        <v>400</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A166A7D5-6EE6-4086-8AED-0FE7228FE728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CA74B3-BC61-44DA-A973-C9279C8C8DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3696,26 +3696,50 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B62" s="14">
+        <v>350</v>
+      </c>
+      <c r="C62" s="14">
+        <v>45</v>
+      </c>
+      <c r="D62" s="14">
+        <v>55</v>
+      </c>
+      <c r="E62" s="14">
+        <v>40</v>
+      </c>
+      <c r="F62" s="14">
+        <v>350</v>
+      </c>
+      <c r="G62" s="14">
+        <v>7</v>
+      </c>
+      <c r="H62" s="14">
+        <v>450</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CA74B3-BC61-44DA-A973-C9279C8C8DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DD35BA-55D3-46C3-A1A1-15283D8402E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3742,26 +3742,50 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B63" s="14">
+        <v>400</v>
+      </c>
+      <c r="C63" s="14">
+        <v>50</v>
+      </c>
+      <c r="D63" s="14">
+        <v>70</v>
+      </c>
+      <c r="E63" s="14">
+        <v>55</v>
+      </c>
+      <c r="F63" s="14">
+        <v>350</v>
+      </c>
+      <c r="G63" s="14">
+        <v>7</v>
+      </c>
+      <c r="H63" s="14">
+        <v>425</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DD35BA-55D3-46C3-A1A1-15283D8402E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6F9C06-89D7-48CA-8DB2-ED573E64BDE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>Start study</t>
+  </si>
+  <si>
+    <t>prepare for exam</t>
   </si>
 </sst>
 </file>
@@ -3788,26 +3791,50 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B64" s="14">
+        <v>350</v>
+      </c>
+      <c r="C64" s="14">
+        <v>60</v>
+      </c>
+      <c r="D64" s="14">
+        <v>85</v>
+      </c>
+      <c r="E64" s="14">
+        <v>40</v>
+      </c>
+      <c r="F64" s="14">
+        <v>150</v>
+      </c>
+      <c r="G64" s="14">
+        <v>3</v>
+      </c>
+      <c r="H64" s="14">
+        <v>350</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>405</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6F9C06-89D7-48CA-8DB2-ED573E64BDE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C11EC60-2581-496C-8835-4CFEF3E569A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3837,26 +3837,50 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B65" s="14">
+        <v>400</v>
+      </c>
+      <c r="C65" s="14">
+        <v>35</v>
+      </c>
+      <c r="D65" s="14">
+        <v>70</v>
+      </c>
+      <c r="E65" s="14">
+        <v>30</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>300</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>835</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>605</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C11EC60-2581-496C-8835-4CFEF3E569A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6A0D46-5226-4597-A2D5-CD648393B1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>prepare for exam</t>
+  </si>
+  <si>
+    <t>Prepare for exam</t>
   </si>
 </sst>
 </file>
@@ -3883,26 +3886,50 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B66" s="14">
+        <v>340</v>
+      </c>
+      <c r="C66" s="14">
+        <v>30</v>
+      </c>
+      <c r="D66" s="14">
+        <v>90</v>
+      </c>
+      <c r="E66" s="14">
+        <v>40</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>400</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6A0D46-5226-4597-A2D5-CD648393B1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CE2BAA-477C-48DE-A2AC-BA4EF3FDFE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3932,26 +3932,50 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B67" s="14">
+        <v>300</v>
+      </c>
+      <c r="C67" s="14">
+        <v>50</v>
+      </c>
+      <c r="D67" s="14">
+        <v>120</v>
+      </c>
+      <c r="E67" s="14">
+        <v>20</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>300</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>650</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CE2BAA-477C-48DE-A2AC-BA4EF3FDFE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF67C0CE-F3C3-4C8C-8C0D-93E1F0C3E157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3978,26 +3978,50 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B68" s="14">
+        <v>300</v>
+      </c>
+      <c r="C68" s="14">
+        <v>60</v>
+      </c>
+      <c r="D68" s="14">
+        <v>300</v>
+      </c>
+      <c r="E68" s="14">
+        <v>50</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>500</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF67C0CE-F3C3-4C8C-8C0D-93E1F0C3E157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDF8D07-9E85-4E78-981A-42475E2D201D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Prepare for exam</t>
+  </si>
+  <si>
+    <t>Prerpare for exam</t>
   </si>
 </sst>
 </file>
@@ -4024,26 +4027,50 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B69" s="14">
+        <v>300</v>
+      </c>
+      <c r="C69" s="14">
+        <v>40</v>
+      </c>
+      <c r="D69" s="14">
+        <v>320</v>
+      </c>
+      <c r="E69" s="14">
+        <v>60</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>450</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDF8D07-9E85-4E78-981A-42475E2D201D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C170C72-04D7-43DD-9BDE-9A3B6C9353E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>Prerpare for exam</t>
+  </si>
+  <si>
+    <t>Next exam</t>
   </si>
 </sst>
 </file>
@@ -4073,26 +4076,50 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B70" s="14">
+        <v>350</v>
+      </c>
+      <c r="C70" s="14">
+        <v>20</v>
+      </c>
+      <c r="D70" s="14">
+        <v>300</v>
+      </c>
+      <c r="E70" s="14">
+        <v>20</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>500</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C170C72-04D7-43DD-9BDE-9A3B6C9353E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747BCB5E-925C-44FC-ABCE-EA1633C7EF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>Next exam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exam </t>
   </si>
 </sst>
 </file>
@@ -4122,26 +4125,50 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B71" s="14">
+        <v>300</v>
+      </c>
+      <c r="C71" s="14">
+        <v>30</v>
+      </c>
+      <c r="D71" s="14">
+        <v>450</v>
+      </c>
+      <c r="E71" s="14">
+        <v>40</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>400</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747BCB5E-925C-44FC-ABCE-EA1633C7EF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738F25E5-577A-4A2E-A844-2540ADE968C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t xml:space="preserve">Exam </t>
+  </si>
+  <si>
+    <t>good</t>
   </si>
 </sst>
 </file>
@@ -4171,26 +4174,50 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B72" s="14">
+        <v>250</v>
+      </c>
+      <c r="C72" s="14">
+        <v>50</v>
+      </c>
+      <c r="D72" s="14">
+        <v>400</v>
+      </c>
+      <c r="E72" s="14">
+        <v>50</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>350</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738F25E5-577A-4A2E-A844-2540ADE968C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CD1B37-ABFE-427D-B26E-A788E1B61E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>good</t>
+  </si>
+  <si>
+    <t>Finaly exam end</t>
   </si>
 </sst>
 </file>
@@ -4220,26 +4223,50 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B73" s="14">
+        <v>300</v>
+      </c>
+      <c r="C73" s="14">
+        <v>50</v>
+      </c>
+      <c r="D73" s="14">
+        <v>500</v>
+      </c>
+      <c r="E73" s="14">
+        <v>40</v>
+      </c>
+      <c r="F73" s="14">
+        <v>0</v>
+      </c>
+      <c r="G73" s="14">
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>250</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CD1B37-ABFE-427D-B26E-A788E1B61E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1E4728-B7E6-4996-8BF1-6D1978950BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>Finaly exam end</t>
+  </si>
+  <si>
+    <t>6+0</t>
   </si>
 </sst>
 </file>
@@ -4269,26 +4272,50 @@
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B74" s="14">
+        <v>250</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D74" s="14">
+        <v>400</v>
+      </c>
+      <c r="E74" s="14">
+        <v>80</v>
+      </c>
+      <c r="F74" s="14">
+        <v>0</v>
+      </c>
+      <c r="G74" s="14">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14">
+        <v>300</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1E4728-B7E6-4996-8BF1-6D1978950BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C74BE4-0DE3-424E-9705-55EB9AB02B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -364,7 +364,7 @@
     <t>Finaly exam end</t>
   </si>
   <si>
-    <t>6+0</t>
+    <t>continue class</t>
   </si>
 </sst>
 </file>
@@ -4278,8 +4278,8 @@
       <c r="B74" s="14">
         <v>250</v>
       </c>
-      <c r="C74" s="14" t="s">
-        <v>109</v>
+      <c r="C74" s="14">
+        <v>60</v>
       </c>
       <c r="D74" s="14">
         <v>400</v>
@@ -4298,11 +4298,11 @@
       </c>
       <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v>1030</v>
+        <v>1090</v>
       </c>
       <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v>410</v>
+        <v>350</v>
       </c>
       <c r="K74" s="16" t="s">
         <v>49</v>
@@ -4318,26 +4318,50 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B75" s="14">
+        <v>300</v>
+      </c>
+      <c r="C75" s="14">
+        <v>20</v>
+      </c>
+      <c r="D75" s="14">
+        <v>50</v>
+      </c>
+      <c r="E75" s="14">
+        <v>60</v>
+      </c>
+      <c r="F75" s="14">
+        <v>1</v>
+      </c>
+      <c r="G75" s="14">
+        <v>50</v>
+      </c>
+      <c r="H75" s="14">
+        <v>320</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>751</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
+        <v>689</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N75" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C74BE4-0DE3-424E-9705-55EB9AB02B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAD87B2-29D3-44B6-8CF3-D7F6884E37DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4364,26 +4364,50 @@
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B76" s="14">
+        <v>350</v>
+      </c>
+      <c r="C76" s="14">
+        <v>40</v>
+      </c>
+      <c r="D76" s="14">
+        <v>80</v>
+      </c>
+      <c r="E76" s="14">
+        <v>40</v>
+      </c>
+      <c r="F76" s="14">
+        <v>0</v>
+      </c>
+      <c r="G76" s="14">
+        <v>0</v>
+      </c>
+      <c r="H76" s="14">
+        <v>300</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N76" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAD87B2-29D3-44B6-8CF3-D7F6884E37DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA67C22E-BB57-4BA7-9D3E-38CEF79B345C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>continue class</t>
+  </si>
+  <si>
+    <t>Work on project</t>
   </si>
 </sst>
 </file>
@@ -4410,26 +4413,50 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="A77" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B77" s="14">
+        <v>300</v>
+      </c>
+      <c r="C77" s="14">
+        <v>60</v>
+      </c>
+      <c r="D77" s="14">
+        <v>50</v>
+      </c>
+      <c r="E77" s="14">
+        <v>50</v>
+      </c>
+      <c r="F77" s="14">
+        <v>6</v>
+      </c>
+      <c r="G77" s="14">
+        <v>300</v>
+      </c>
+      <c r="H77" s="14">
+        <v>400</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>866</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="17"/>
+        <v>574</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N77" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA67C22E-BB57-4BA7-9D3E-38CEF79B345C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE912DD-FED7-43F4-BEE1-D4036EA607D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4459,26 +4459,50 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+      <c r="A78" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B78" s="14">
+        <v>260</v>
+      </c>
+      <c r="C78" s="14">
+        <v>55</v>
+      </c>
+      <c r="D78" s="14">
+        <v>80</v>
+      </c>
+      <c r="E78" s="14">
+        <v>70</v>
+      </c>
+      <c r="F78" s="14">
+        <v>3</v>
+      </c>
+      <c r="G78" s="14">
+        <v>150</v>
+      </c>
+      <c r="H78" s="14">
+        <v>450</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>918</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="17"/>
+        <v>522</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N78" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE912DD-FED7-43F4-BEE1-D4036EA607D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8737976C-5964-4602-9ED2-002C8C0B03AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4505,26 +4505,50 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+      <c r="A79" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B79" s="14">
+        <v>280</v>
+      </c>
+      <c r="C79" s="14">
+        <v>30</v>
+      </c>
+      <c r="D79" s="14">
+        <v>50</v>
+      </c>
+      <c r="E79" s="14">
+        <v>40</v>
+      </c>
+      <c r="F79" s="14">
+        <v>3</v>
+      </c>
+      <c r="G79" s="14">
+        <v>150</v>
+      </c>
+      <c r="H79" s="14">
+        <v>400</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>803</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
-      <c r="N79" s="17"/>
+        <v>637</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N79" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8737976C-5964-4602-9ED2-002C8C0B03AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC16C76E-F307-4DD1-A3FA-04E3D56C72D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>Work on project</t>
+  </si>
+  <si>
+    <t>Extra class</t>
   </si>
 </sst>
 </file>
@@ -4551,26 +4554,50 @@
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="15" t="str">
+      <c r="A80" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B80" s="14">
+        <v>320</v>
+      </c>
+      <c r="C80" s="14">
+        <v>20</v>
+      </c>
+      <c r="D80" s="14">
+        <v>60</v>
+      </c>
+      <c r="E80" s="14">
+        <v>80</v>
+      </c>
+      <c r="F80" s="14">
+        <v>2</v>
+      </c>
+      <c r="G80" s="14">
+        <v>100</v>
+      </c>
+      <c r="H80" s="14">
+        <v>350</v>
+      </c>
+      <c r="I80" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="15" t="str">
+        <v>832</v>
+      </c>
+      <c r="J80" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
-      <c r="N80" s="17"/>
+        <v>608</v>
+      </c>
+      <c r="K80" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L80" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M80" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N80" s="17" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC16C76E-F307-4DD1-A3FA-04E3D56C72D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE4D4DF-49AE-439A-8411-07A24D39659C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>Extra class</t>
+  </si>
+  <si>
+    <t>Rest day</t>
   </si>
 </sst>
 </file>
@@ -4600,26 +4603,50 @@
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="13"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="15" t="str">
+      <c r="A81" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B81" s="14">
+        <v>400</v>
+      </c>
+      <c r="C81" s="14">
+        <v>60</v>
+      </c>
+      <c r="D81" s="14">
+        <v>45</v>
+      </c>
+      <c r="E81" s="14">
+        <v>70</v>
+      </c>
+      <c r="F81" s="14">
+        <v>0</v>
+      </c>
+      <c r="G81" s="14">
+        <v>0</v>
+      </c>
+      <c r="H81" s="14">
+        <v>365</v>
+      </c>
+      <c r="I81" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J81" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
-      <c r="N81" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K81" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M81" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N81" s="17" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE4D4DF-49AE-439A-8411-07A24D39659C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D086B3E4-4FBE-4529-94F8-DAEEC7EC59C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>Rest day</t>
+  </si>
+  <si>
+    <t>Study continue</t>
   </si>
 </sst>
 </file>
@@ -4649,26 +4652,50 @@
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" s="13"/>
-      <c r="B82" s="14"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="15" t="str">
+      <c r="A82" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B82" s="14">
+        <v>455</v>
+      </c>
+      <c r="C82" s="14">
+        <v>20</v>
+      </c>
+      <c r="D82" s="14">
+        <v>60</v>
+      </c>
+      <c r="E82" s="14">
+        <v>40</v>
+      </c>
+      <c r="F82" s="14">
+        <v>0</v>
+      </c>
+      <c r="G82" s="14">
+        <v>0</v>
+      </c>
+      <c r="H82" s="14">
+        <v>400</v>
+      </c>
+      <c r="I82" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="15" t="str">
+        <v>975</v>
+      </c>
+      <c r="J82" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="16"/>
-      <c r="N82" s="17"/>
+        <v>465</v>
+      </c>
+      <c r="K82" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L82" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M82" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N82" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D086B3E4-4FBE-4529-94F8-DAEEC7EC59C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BBB8E7-6279-4FF4-B6B4-E2662B3EB647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4698,26 +4698,50 @@
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83" s="13"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="15" t="str">
+      <c r="A83" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B83" s="14">
+        <v>320</v>
+      </c>
+      <c r="C83" s="14">
+        <v>40</v>
+      </c>
+      <c r="D83" s="14">
+        <v>45</v>
+      </c>
+      <c r="E83" s="14">
+        <v>50</v>
+      </c>
+      <c r="F83" s="14">
+        <v>6</v>
+      </c>
+      <c r="G83" s="14">
+        <v>300</v>
+      </c>
+      <c r="H83" s="14">
+        <v>350</v>
+      </c>
+      <c r="I83" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="15" t="str">
+        <v>811</v>
+      </c>
+      <c r="J83" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
-      <c r="N83" s="17"/>
+        <v>629</v>
+      </c>
+      <c r="K83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L83" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M83" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N83" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BBB8E7-6279-4FF4-B6B4-E2662B3EB647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8B42C7-BF65-4FC1-ABCC-5A75B1236886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4744,26 +4744,50 @@
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A84" s="13"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="15" t="str">
+      <c r="A84" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B84" s="14">
+        <v>300</v>
+      </c>
+      <c r="C84" s="14">
+        <v>60</v>
+      </c>
+      <c r="D84" s="14">
+        <v>80</v>
+      </c>
+      <c r="E84" s="14">
+        <v>30</v>
+      </c>
+      <c r="F84" s="14">
+        <v>6</v>
+      </c>
+      <c r="G84" s="14">
+        <v>300</v>
+      </c>
+      <c r="H84" s="14">
+        <v>420</v>
+      </c>
+      <c r="I84" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="15" t="str">
+        <v>896</v>
+      </c>
+      <c r="J84" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="16"/>
-      <c r="N84" s="17"/>
+        <v>544</v>
+      </c>
+      <c r="K84" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L84" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M84" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N84" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8B42C7-BF65-4FC1-ABCC-5A75B1236886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FCABF3-FEA0-45DB-9941-A34DEC0E3FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t>Study continue</t>
+  </si>
+  <si>
+    <t>GOOD DAY</t>
   </si>
 </sst>
 </file>
@@ -4790,26 +4793,50 @@
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A85" s="13"/>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-      <c r="I85" s="15" t="str">
+      <c r="A85" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B85" s="14">
+        <v>350</v>
+      </c>
+      <c r="C85" s="14">
+        <v>30</v>
+      </c>
+      <c r="D85" s="14">
+        <v>40</v>
+      </c>
+      <c r="E85" s="14">
+        <v>50</v>
+      </c>
+      <c r="F85" s="14">
+        <v>3</v>
+      </c>
+      <c r="G85" s="14">
+        <v>150</v>
+      </c>
+      <c r="H85" s="14">
+        <v>400</v>
+      </c>
+      <c r="I85" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="15" t="str">
+        <v>873</v>
+      </c>
+      <c r="J85" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K85" s="16"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="16"/>
-      <c r="N85" s="17"/>
+        <v>567</v>
+      </c>
+      <c r="K85" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L85" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M85" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N85" s="17" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="13"/>
